--- a/public/templates/cpac-tracker.xlsx
+++ b/public/templates/cpac-tracker.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <r>
       <rPr>
@@ -73,37 +73,13 @@
     <t>Q2 2025</t>
   </si>
   <si>
-    <t>2025-04-01</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
     <t>Q3 2025</t>
   </si>
   <si>
-    <t>2025-07-01</t>
-  </si>
-  <si>
-    <t>2025-09-30</t>
-  </si>
-  <si>
     <t>Q4 2025</t>
   </si>
   <si>
-    <t>2025-10-01</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
     <t>Q1 2026</t>
-  </si>
-  <si>
-    <t>2026-01-01</t>
-  </si>
-  <si>
-    <t>2026-03-31</t>
   </si>
   <si>
     <t>Formulas: Total cost = sum of the five components. CPAC = Total cost ÷ Accepted change units. Δ = (CPAC_n − CPAC_{n-1}) ÷ CPAC_{n-1}. See the Instructions tab.</t>
@@ -212,9 +188,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="+0.0%;-0.0%;0.0%"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="+0.0%;-0.0%;0.0%"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -315,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -327,21 +304,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -774,409 +754,409 @@
       <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="B3" s="4">
+        <v>45748</v>
+      </c>
+      <c r="C3" s="4">
+        <v>45838</v>
+      </c>
+      <c r="D3" s="5">
         <v>800</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="5">
         <v>350</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="5">
         <v>22000</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="5">
         <v>7500</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="5">
         <v>4200</v>
       </c>
-      <c r="I3" s="5">
-        <f>D3+E3+F3+G3+H3</f>
-      </c>
-      <c r="J3" s="6">
+      <c r="I3" s="6">
+        <f>IF(SUM(D3:H3)=0,"",D3+E3+F3+G3+H3)</f>
+      </c>
+      <c r="J3" s="7">
         <v>38</v>
       </c>
-      <c r="K3" s="5">
-        <f>IF(J3=0,"",I3/J3)</f>
-      </c>
-      <c r="L3" s="7">
+      <c r="K3" s="6">
+        <f>IF(OR(I3="",J3="",J3=0),"",I3/J3)</f>
+      </c>
+      <c r="L3" s="8">
         <f>""</f>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="4">
+        <v>14</v>
+      </c>
+      <c r="B4" s="4">
+        <v>45839</v>
+      </c>
+      <c r="C4" s="4">
+        <v>45930</v>
+      </c>
+      <c r="D4" s="5">
         <v>1450</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <v>380</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="5">
         <v>22500</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="5">
         <v>8200</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="5">
         <v>5100</v>
       </c>
-      <c r="I4" s="5">
-        <f>D4+E4+F4+G4+H4</f>
-      </c>
-      <c r="J4" s="6">
+      <c r="I4" s="6">
+        <f>IF(SUM(D4:H4)=0,"",D4+E4+F4+G4+H4)</f>
+      </c>
+      <c r="J4" s="7">
         <v>44</v>
       </c>
-      <c r="K4" s="5">
-        <f>IF(J4=0,"",I4/J4)</f>
-      </c>
-      <c r="L4" s="7">
+      <c r="K4" s="6">
+        <f>IF(OR(I4="",J4="",J4=0),"",I4/J4)</f>
+      </c>
+      <c r="L4" s="8">
         <f>IF(OR(K4="",K3=""),"",(K4-K3)/K3)</f>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="4">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4">
+        <v>45931</v>
+      </c>
+      <c r="C5" s="4">
+        <v>46022</v>
+      </c>
+      <c r="D5" s="5">
         <v>1620</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="5">
         <v>410</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="5">
         <v>21800</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="5">
         <v>7800</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="5">
         <v>4100</v>
       </c>
-      <c r="I5" s="5">
-        <f>D5+E5+F5+G5+H5</f>
-      </c>
-      <c r="J5" s="6">
+      <c r="I5" s="6">
+        <f>IF(SUM(D5:H5)=0,"",D5+E5+F5+G5+H5)</f>
+      </c>
+      <c r="J5" s="7">
         <v>51</v>
       </c>
-      <c r="K5" s="5">
-        <f>IF(J5=0,"",I5/J5)</f>
-      </c>
-      <c r="L5" s="7">
+      <c r="K5" s="6">
+        <f>IF(OR(I5="",J5="",J5=0),"",I5/J5)</f>
+      </c>
+      <c r="L5" s="8">
         <f>IF(OR(K5="",K4=""),"",(K5-K4)/K4)</f>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="4">
+        <v>16</v>
+      </c>
+      <c r="B6" s="4">
+        <v>46023</v>
+      </c>
+      <c r="C6" s="4">
+        <v>46112</v>
+      </c>
+      <c r="D6" s="5">
         <v>1700</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="5">
         <v>420</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="5">
         <v>21000</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="5">
         <v>7100</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="5">
         <v>2800</v>
       </c>
-      <c r="I6" s="5">
-        <f>D6+E6+F6+G6+H6</f>
-      </c>
-      <c r="J6" s="6">
+      <c r="I6" s="6">
+        <f>IF(SUM(D6:H6)=0,"",D6+E6+F6+G6+H6)</f>
+      </c>
+      <c r="J6" s="7">
         <v>58</v>
       </c>
-      <c r="K6" s="5">
-        <f>IF(J6=0,"",I6/J6)</f>
-      </c>
-      <c r="L6" s="7">
+      <c r="K6" s="6">
+        <f>IF(OR(I6="",J6="",J6=0),"",I6/J6)</f>
+      </c>
+      <c r="L6" s="8">
         <f>IF(OR(K6="",K5=""),"",(K6-K5)/K5)</f>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="8">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="9">
         <f>IF(SUM(D7:H7)=0,"",D7+E7+F7+G7+H7)</f>
       </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="8">
+      <c r="J7" s="7"/>
+      <c r="K7" s="9">
         <f>IF(OR(I7="",J7="",J7=0),"",I7/J7)</f>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="10">
         <f>IF(OR(K7="",K6=""),"",(K7-K6)/K6)</f>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="8">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="9">
         <f>IF(SUM(D8:H8)=0,"",D8+E8+F8+G8+H8)</f>
       </c>
-      <c r="J8" s="6"/>
-      <c r="K8" s="8">
+      <c r="J8" s="7"/>
+      <c r="K8" s="9">
         <f>IF(OR(I8="",J8="",J8=0),"",I8/J8)</f>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="10">
         <f>IF(OR(K8="",K7=""),"",(K8-K7)/K7)</f>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="8">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="9">
         <f>IF(SUM(D9:H9)=0,"",D9+E9+F9+G9+H9)</f>
       </c>
-      <c r="J9" s="6"/>
-      <c r="K9" s="8">
+      <c r="J9" s="7"/>
+      <c r="K9" s="9">
         <f>IF(OR(I9="",J9="",J9=0),"",I9/J9)</f>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="10">
         <f>IF(OR(K9="",K8=""),"",(K9-K8)/K8)</f>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="8">
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="9">
         <f>IF(SUM(D10:H10)=0,"",D10+E10+F10+G10+H10)</f>
       </c>
-      <c r="J10" s="6"/>
-      <c r="K10" s="8">
+      <c r="J10" s="7"/>
+      <c r="K10" s="9">
         <f>IF(OR(I10="",J10="",J10=0),"",I10/J10)</f>
       </c>
-      <c r="L10" s="9">
+      <c r="L10" s="10">
         <f>IF(OR(K10="",K9=""),"",(K10-K9)/K9)</f>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="8">
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="9">
         <f>IF(SUM(D11:H11)=0,"",D11+E11+F11+G11+H11)</f>
       </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="8">
+      <c r="J11" s="7"/>
+      <c r="K11" s="9">
         <f>IF(OR(I11="",J11="",J11=0),"",I11/J11)</f>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="10">
         <f>IF(OR(K11="",K10=""),"",(K11-K10)/K10)</f>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="8">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="9">
         <f>IF(SUM(D12:H12)=0,"",D12+E12+F12+G12+H12)</f>
       </c>
-      <c r="J12" s="6"/>
-      <c r="K12" s="8">
+      <c r="J12" s="7"/>
+      <c r="K12" s="9">
         <f>IF(OR(I12="",J12="",J12=0),"",I12/J12)</f>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="10">
         <f>IF(OR(K12="",K11=""),"",(K12-K11)/K11)</f>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="8">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="9">
         <f>IF(SUM(D13:H13)=0,"",D13+E13+F13+G13+H13)</f>
       </c>
-      <c r="J13" s="6"/>
-      <c r="K13" s="8">
+      <c r="J13" s="7"/>
+      <c r="K13" s="9">
         <f>IF(OR(I13="",J13="",J13=0),"",I13/J13)</f>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="10">
         <f>IF(OR(K13="",K12=""),"",(K13-K12)/K12)</f>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="8">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="9">
         <f>IF(SUM(D14:H14)=0,"",D14+E14+F14+G14+H14)</f>
       </c>
-      <c r="J14" s="6"/>
-      <c r="K14" s="8">
+      <c r="J14" s="7"/>
+      <c r="K14" s="9">
         <f>IF(OR(I14="",J14="",J14=0),"",I14/J14)</f>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="10">
         <f>IF(OR(K14="",K13=""),"",(K14-K13)/K13)</f>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="8">
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="9">
         <f>IF(SUM(D15:H15)=0,"",D15+E15+F15+G15+H15)</f>
       </c>
-      <c r="J15" s="6"/>
-      <c r="K15" s="8">
+      <c r="J15" s="7"/>
+      <c r="K15" s="9">
         <f>IF(OR(I15="",J15="",J15=0),"",I15/J15)</f>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="10">
         <f>IF(OR(K15="",K14=""),"",(K15-K14)/K14)</f>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="8">
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="9">
         <f>IF(SUM(D16:H16)=0,"",D16+E16+F16+G16+H16)</f>
       </c>
-      <c r="J16" s="6"/>
-      <c r="K16" s="8">
+      <c r="J16" s="7"/>
+      <c r="K16" s="9">
         <f>IF(OR(I16="",J16="",J16=0),"",I16/J16)</f>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="10">
         <f>IF(OR(K16="",K15=""),"",(K16-K15)/K15)</f>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="8">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="9">
         <f>IF(SUM(D17:H17)=0,"",D17+E17+F17+G17+H17)</f>
       </c>
-      <c r="J17" s="6"/>
-      <c r="K17" s="8">
+      <c r="J17" s="7"/>
+      <c r="K17" s="9">
         <f>IF(OR(I17="",J17="",J17=0),"",I17/J17)</f>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="10">
         <f>IF(OR(K17="",K16=""),"",(K17-K16)/K16)</f>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="8">
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="9">
         <f>IF(SUM(D18:H18)=0,"",D18+E18+F18+G18+H18)</f>
       </c>
-      <c r="J18" s="6"/>
-      <c r="K18" s="8">
+      <c r="J18" s="7"/>
+      <c r="K18" s="9">
         <f>IF(OR(I18="",J18="",J18=0),"",I18/J18)</f>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="10">
         <f>IF(OR(K18="",K17=""),"",(K18-K17)/K17)</f>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
+      <c r="A20" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1217,168 +1197,168 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+    <row r="12" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+    <row r="13" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+    <row r="14" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+    <row r="15" ht="44" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+    <row r="16" ht="44" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+    <row r="17" ht="44" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+    <row r="18" ht="44" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+    <row r="19" ht="44" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+    <row r="20" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+    <row r="21" ht="66" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+    <row r="22" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+    <row r="23" ht="44" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+    <row r="25" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+    <row r="26" ht="66" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+    <row r="27" ht="44" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+    <row r="28" ht="44" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+    <row r="29" ht="44" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+    <row r="31" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+    <row r="32" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+    <row r="33" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
+    <row r="34" ht="44" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="26" ht="54" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+    <row r="35" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="27" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
+    <row r="36" ht="44" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="28" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
+    <row r="37" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/public/templates/cpac-tracker.xlsx
+++ b/public/templates/cpac-tracker.xlsx
@@ -776,16 +776,16 @@
         <v>4200</v>
       </c>
       <c r="I3" s="6">
-        <f>IF(SUM(D3:H3)=0,"",D3+E3+F3+G3+H3)</f>
+        <f>IFERROR(IF(SUM(D3:H3)=0,NA(),D3+E3+F3+G3+H3),NA())</f>
       </c>
       <c r="J3" s="7">
         <v>38</v>
       </c>
       <c r="K3" s="6">
-        <f>IF(OR(I3="",J3="",J3=0),"",I3/J3)</f>
+        <f>IFERROR(IF(OR(ISNA(I3),ISBLANK(J3),J3=0),NA(),I3/J3),NA())</f>
       </c>
       <c r="L3" s="8">
-        <f>""</f>
+        <f>NA()</f>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -814,16 +814,16 @@
         <v>5100</v>
       </c>
       <c r="I4" s="6">
-        <f>IF(SUM(D4:H4)=0,"",D4+E4+F4+G4+H4)</f>
+        <f>IFERROR(IF(SUM(D4:H4)=0,NA(),D4+E4+F4+G4+H4),NA())</f>
       </c>
       <c r="J4" s="7">
         <v>44</v>
       </c>
       <c r="K4" s="6">
-        <f>IF(OR(I4="",J4="",J4=0),"",I4/J4)</f>
+        <f>IFERROR(IF(OR(ISNA(I4),ISBLANK(J4),J4=0),NA(),I4/J4),NA())</f>
       </c>
       <c r="L4" s="8">
-        <f>IF(OR(K4="",K3=""),"",(K4-K3)/K3)</f>
+        <f>IFERROR(IF(OR(ISNA(K4),ISNA(K3)),NA(),(K4-K3)/K3),NA())</f>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -852,16 +852,16 @@
         <v>4100</v>
       </c>
       <c r="I5" s="6">
-        <f>IF(SUM(D5:H5)=0,"",D5+E5+F5+G5+H5)</f>
+        <f>IFERROR(IF(SUM(D5:H5)=0,NA(),D5+E5+F5+G5+H5),NA())</f>
       </c>
       <c r="J5" s="7">
         <v>51</v>
       </c>
       <c r="K5" s="6">
-        <f>IF(OR(I5="",J5="",J5=0),"",I5/J5)</f>
+        <f>IFERROR(IF(OR(ISNA(I5),ISBLANK(J5),J5=0),NA(),I5/J5),NA())</f>
       </c>
       <c r="L5" s="8">
-        <f>IF(OR(K5="",K4=""),"",(K5-K4)/K4)</f>
+        <f>IFERROR(IF(OR(ISNA(K5),ISNA(K4)),NA(),(K5-K4)/K4),NA())</f>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -890,16 +890,16 @@
         <v>2800</v>
       </c>
       <c r="I6" s="6">
-        <f>IF(SUM(D6:H6)=0,"",D6+E6+F6+G6+H6)</f>
+        <f>IFERROR(IF(SUM(D6:H6)=0,NA(),D6+E6+F6+G6+H6),NA())</f>
       </c>
       <c r="J6" s="7">
         <v>58</v>
       </c>
       <c r="K6" s="6">
-        <f>IF(OR(I6="",J6="",J6=0),"",I6/J6)</f>
+        <f>IFERROR(IF(OR(ISNA(I6),ISBLANK(J6),J6=0),NA(),I6/J6),NA())</f>
       </c>
       <c r="L6" s="8">
-        <f>IF(OR(K6="",K5=""),"",(K6-K5)/K5)</f>
+        <f>IFERROR(IF(OR(ISNA(K6),ISNA(K5)),NA(),(K6-K5)/K5),NA())</f>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -912,14 +912,14 @@
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="9">
-        <f>IF(SUM(D7:H7)=0,"",D7+E7+F7+G7+H7)</f>
+        <f>IFERROR(IF(SUM(D7:H7)=0,NA(),D7+E7+F7+G7+H7),NA())</f>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="9">
-        <f>IF(OR(I7="",J7="",J7=0),"",I7/J7)</f>
+        <f>IFERROR(IF(OR(ISNA(I7),ISBLANK(J7),J7=0),NA(),I7/J7),NA())</f>
       </c>
       <c r="L7" s="10">
-        <f>IF(OR(K7="",K6=""),"",(K7-K6)/K6)</f>
+        <f>IFERROR(IF(OR(ISNA(K7),ISNA(K6)),NA(),(K7-K6)/K6),NA())</f>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -932,14 +932,14 @@
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
       <c r="I8" s="9">
-        <f>IF(SUM(D8:H8)=0,"",D8+E8+F8+G8+H8)</f>
+        <f>IFERROR(IF(SUM(D8:H8)=0,NA(),D8+E8+F8+G8+H8),NA())</f>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="9">
-        <f>IF(OR(I8="",J8="",J8=0),"",I8/J8)</f>
+        <f>IFERROR(IF(OR(ISNA(I8),ISBLANK(J8),J8=0),NA(),I8/J8),NA())</f>
       </c>
       <c r="L8" s="10">
-        <f>IF(OR(K8="",K7=""),"",(K8-K7)/K7)</f>
+        <f>IFERROR(IF(OR(ISNA(K8),ISNA(K7)),NA(),(K8-K7)/K7),NA())</f>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -952,14 +952,14 @@
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="9">
-        <f>IF(SUM(D9:H9)=0,"",D9+E9+F9+G9+H9)</f>
+        <f>IFERROR(IF(SUM(D9:H9)=0,NA(),D9+E9+F9+G9+H9),NA())</f>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="9">
-        <f>IF(OR(I9="",J9="",J9=0),"",I9/J9)</f>
+        <f>IFERROR(IF(OR(ISNA(I9),ISBLANK(J9),J9=0),NA(),I9/J9),NA())</f>
       </c>
       <c r="L9" s="10">
-        <f>IF(OR(K9="",K8=""),"",(K9-K8)/K8)</f>
+        <f>IFERROR(IF(OR(ISNA(K9),ISNA(K8)),NA(),(K9-K8)/K8),NA())</f>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -972,14 +972,14 @@
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="9">
-        <f>IF(SUM(D10:H10)=0,"",D10+E10+F10+G10+H10)</f>
+        <f>IFERROR(IF(SUM(D10:H10)=0,NA(),D10+E10+F10+G10+H10),NA())</f>
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="9">
-        <f>IF(OR(I10="",J10="",J10=0),"",I10/J10)</f>
+        <f>IFERROR(IF(OR(ISNA(I10),ISBLANK(J10),J10=0),NA(),I10/J10),NA())</f>
       </c>
       <c r="L10" s="10">
-        <f>IF(OR(K10="",K9=""),"",(K10-K9)/K9)</f>
+        <f>IFERROR(IF(OR(ISNA(K10),ISNA(K9)),NA(),(K10-K9)/K9),NA())</f>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -992,14 +992,14 @@
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="9">
-        <f>IF(SUM(D11:H11)=0,"",D11+E11+F11+G11+H11)</f>
+        <f>IFERROR(IF(SUM(D11:H11)=0,NA(),D11+E11+F11+G11+H11),NA())</f>
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="9">
-        <f>IF(OR(I11="",J11="",J11=0),"",I11/J11)</f>
+        <f>IFERROR(IF(OR(ISNA(I11),ISBLANK(J11),J11=0),NA(),I11/J11),NA())</f>
       </c>
       <c r="L11" s="10">
-        <f>IF(OR(K11="",K10=""),"",(K11-K10)/K10)</f>
+        <f>IFERROR(IF(OR(ISNA(K11),ISNA(K10)),NA(),(K11-K10)/K10),NA())</f>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1012,14 +1012,14 @@
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="9">
-        <f>IF(SUM(D12:H12)=0,"",D12+E12+F12+G12+H12)</f>
+        <f>IFERROR(IF(SUM(D12:H12)=0,NA(),D12+E12+F12+G12+H12),NA())</f>
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="9">
-        <f>IF(OR(I12="",J12="",J12=0),"",I12/J12)</f>
+        <f>IFERROR(IF(OR(ISNA(I12),ISBLANK(J12),J12=0),NA(),I12/J12),NA())</f>
       </c>
       <c r="L12" s="10">
-        <f>IF(OR(K12="",K11=""),"",(K12-K11)/K11)</f>
+        <f>IFERROR(IF(OR(ISNA(K12),ISNA(K11)),NA(),(K12-K11)/K11),NA())</f>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1032,14 +1032,14 @@
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="9">
-        <f>IF(SUM(D13:H13)=0,"",D13+E13+F13+G13+H13)</f>
+        <f>IFERROR(IF(SUM(D13:H13)=0,NA(),D13+E13+F13+G13+H13),NA())</f>
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="9">
-        <f>IF(OR(I13="",J13="",J13=0),"",I13/J13)</f>
+        <f>IFERROR(IF(OR(ISNA(I13),ISBLANK(J13),J13=0),NA(),I13/J13),NA())</f>
       </c>
       <c r="L13" s="10">
-        <f>IF(OR(K13="",K12=""),"",(K13-K12)/K12)</f>
+        <f>IFERROR(IF(OR(ISNA(K13),ISNA(K12)),NA(),(K13-K12)/K12),NA())</f>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1052,14 +1052,14 @@
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="9">
-        <f>IF(SUM(D14:H14)=0,"",D14+E14+F14+G14+H14)</f>
+        <f>IFERROR(IF(SUM(D14:H14)=0,NA(),D14+E14+F14+G14+H14),NA())</f>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="9">
-        <f>IF(OR(I14="",J14="",J14=0),"",I14/J14)</f>
+        <f>IFERROR(IF(OR(ISNA(I14),ISBLANK(J14),J14=0),NA(),I14/J14),NA())</f>
       </c>
       <c r="L14" s="10">
-        <f>IF(OR(K14="",K13=""),"",(K14-K13)/K13)</f>
+        <f>IFERROR(IF(OR(ISNA(K14),ISNA(K13)),NA(),(K14-K13)/K13),NA())</f>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1072,14 +1072,14 @@
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="9">
-        <f>IF(SUM(D15:H15)=0,"",D15+E15+F15+G15+H15)</f>
+        <f>IFERROR(IF(SUM(D15:H15)=0,NA(),D15+E15+F15+G15+H15),NA())</f>
       </c>
       <c r="J15" s="7"/>
       <c r="K15" s="9">
-        <f>IF(OR(I15="",J15="",J15=0),"",I15/J15)</f>
+        <f>IFERROR(IF(OR(ISNA(I15),ISBLANK(J15),J15=0),NA(),I15/J15),NA())</f>
       </c>
       <c r="L15" s="10">
-        <f>IF(OR(K15="",K14=""),"",(K15-K14)/K14)</f>
+        <f>IFERROR(IF(OR(ISNA(K15),ISNA(K14)),NA(),(K15-K14)/K14),NA())</f>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1092,14 +1092,14 @@
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="9">
-        <f>IF(SUM(D16:H16)=0,"",D16+E16+F16+G16+H16)</f>
+        <f>IFERROR(IF(SUM(D16:H16)=0,NA(),D16+E16+F16+G16+H16),NA())</f>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="9">
-        <f>IF(OR(I16="",J16="",J16=0),"",I16/J16)</f>
+        <f>IFERROR(IF(OR(ISNA(I16),ISBLANK(J16),J16=0),NA(),I16/J16),NA())</f>
       </c>
       <c r="L16" s="10">
-        <f>IF(OR(K16="",K15=""),"",(K16-K15)/K15)</f>
+        <f>IFERROR(IF(OR(ISNA(K16),ISNA(K15)),NA(),(K16-K15)/K15),NA())</f>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1112,14 +1112,14 @@
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="9">
-        <f>IF(SUM(D17:H17)=0,"",D17+E17+F17+G17+H17)</f>
+        <f>IFERROR(IF(SUM(D17:H17)=0,NA(),D17+E17+F17+G17+H17),NA())</f>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="9">
-        <f>IF(OR(I17="",J17="",J17=0),"",I17/J17)</f>
+        <f>IFERROR(IF(OR(ISNA(I17),ISBLANK(J17),J17=0),NA(),I17/J17),NA())</f>
       </c>
       <c r="L17" s="10">
-        <f>IF(OR(K17="",K16=""),"",(K17-K16)/K16)</f>
+        <f>IFERROR(IF(OR(ISNA(K17),ISNA(K16)),NA(),(K17-K16)/K16),NA())</f>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1132,14 +1132,14 @@
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="9">
-        <f>IF(SUM(D18:H18)=0,"",D18+E18+F18+G18+H18)</f>
+        <f>IFERROR(IF(SUM(D18:H18)=0,NA(),D18+E18+F18+G18+H18),NA())</f>
       </c>
       <c r="J18" s="7"/>
       <c r="K18" s="9">
-        <f>IF(OR(I18="",J18="",J18=0),"",I18/J18)</f>
+        <f>IFERROR(IF(OR(ISNA(I18),ISBLANK(J18),J18=0),NA(),I18/J18),NA())</f>
       </c>
       <c r="L18" s="10">
-        <f>IF(OR(K18="",K17=""),"",(K18-K17)/K17)</f>
+        <f>IFERROR(IF(OR(ISNA(K18),ISNA(K17)),NA(),(K18-K17)/K17),NA())</f>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">

--- a/public/templates/cpac-tracker.xlsx
+++ b/public/templates/cpac-tracker.xlsx
@@ -30,7 +30,7 @@
         <sz val="10"/>
         <rFont val="Helvetica"/>
       </rPr>
-      <t>Canonical definition at costperacceptedchange.org</t>
+      <t>Canonical definition at aifinops.dev</t>
     </r>
   </si>
   <si>
@@ -88,7 +88,7 @@
     <t>Cost per accepted change — tracker instructions</t>
   </si>
   <si>
-    <t>Canonical definition: https://costperacceptedchange.org</t>
+    <t>Canonical definition: https://aifinops.dev</t>
   </si>
   <si>
     <t>Defined in The Delivery Gap (Brenn Hill, 2026) as the cost vertex of the Verification Triangle.</t>
@@ -166,19 +166,19 @@
     <t>Where to find help</t>
   </si>
   <si>
-    <t>— Definition and worked example: https://costperacceptedchange.org/</t>
-  </si>
-  <si>
-    <t>— How to use the metric correctly: https://costperacceptedchange.org/use</t>
-  </si>
-  <si>
-    <t>— FAQ, including the git command recipe for counting line changes: https://costperacceptedchange.org/faq</t>
-  </si>
-  <si>
-    <t>— Calculator (single-window): https://costperacceptedchange.org/calculator</t>
-  </si>
-  <si>
-    <t>— Quarterly review template: https://costperacceptedchange.org/templates/quarterly-review</t>
+    <t>— Definition and worked example: https://aifinops.dev/</t>
+  </si>
+  <si>
+    <t>— How to use the metric correctly: https://aifinops.dev/use</t>
+  </si>
+  <si>
+    <t>— FAQ, including the git command recipe for counting line changes: https://aifinops.dev/faq</t>
+  </si>
+  <si>
+    <t>— Calculator (single-window): https://aifinops.dev/calculator</t>
+  </si>
+  <si>
+    <t>— Quarterly review template: https://aifinops.dev/templates/quarterly-review</t>
   </si>
   <si>
     <t>— Source: https://github.com/brennhill/cost-per-accepted-change</t>
@@ -1351,7 +1351,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" ht="44" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>49</v>
       </c>
